--- a/assessment_forms/012_equipment_safety_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/012_equipment_safety_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'equipment',_'value':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Equipment', 'value': 'Equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'machinery',_'value':_'machinery'}</t>
+          <t>machinery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Machinery', 'value': 'Machinery'}</t>
+          <t>Machinery</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tools',_'value':_'tools'}</t>
+          <t>tools</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Tools', 'value': 'Tools'}</t>
+          <t>Tools</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'office',_'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Office', 'value': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'warehouse',_'value':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Warehouse', 'value': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'factory',_'value':_'factory'}</t>
+          <t>factory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Factory', 'value': 'Factory'}</t>
+          <t>Factory</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_required',_'value':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Required', 'value': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_use',_'value':_'in_use'}</t>
+          <t>in_use</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Use', 'value': 'In Use'}</t>
+          <t>In Use</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_in_use',_'value':_'not_in_use'}</t>
+          <t>not_in_use</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not In Use', 'value': 'Not In Use'}</t>
+          <t>Not In Use</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'decommissioned',_'value':_'decommissioned'}</t>
+          <t>decommissioned</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Decommissioned', 'value': 'Decommissioned'}</t>
+          <t>Decommissioned</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'removed',_'value':_'removed'}</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Removed', 'value': 'Removed'}</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
